--- a/agent_runs/manjidiwang/episodes/ep06/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep06/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>郑建国酒桌发威 （，总时长：11秒，镜头数：5个）</t>
+          <t>郑建国酒桌发威</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>郑建国踉跄离去 （，总时长：10秒，镜头数：4个）</t>
+          <t>郑建国踉跄离去</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>郑建国烦躁归家 （，总时长：10秒，镜头数：4个）</t>
+          <t>郑建国烦躁归家</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>黑手伏击 （，总时长：15秒，镜头数：7个）</t>
+          <t>黑手伏击</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>推下灭口 （，总时长：10秒，镜头数：4个）</t>
+          <t>推下灭口</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>惊闻死讯 （，总时长：10秒，镜头数：5个）</t>
+          <t>惊闻死讯</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>邱瑞震怒下令 （，总时长：10秒，镜头数：4个）</t>
+          <t>邱瑞震怒下令</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>危机汇报 （，总时长：10秒，镜头数：5个）</t>
+          <t>危机汇报</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>暗流涌动 （，总时长：11秒，镜头数：5个）</t>
+          <t>暗流涌动</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
